--- a/CinemaReady.xlsx
+++ b/CinemaReady.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CinemaReady-GitHub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\123123123123\CinemaReady-ONE-UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91C58D2-8AA1-40FB-8B9A-A54AA9F24533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095F1F98-4E2E-4A5E-AB74-8087B84723B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CinemaReady" sheetId="1" r:id="rId1"/>
@@ -462,7 +462,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -596,6 +596,11 @@
       <name val="Aptos"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFB8B8B8"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
       <b/>
       <sz val="20"/>
       <color rgb="FFD71920"/>
@@ -605,21 +610,6 @@
       <sz val="10"/>
       <color rgb="FFFFD9DB"/>
       <name val="Aptos"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FFB8B8B8"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFB8B8B8"/>
-      <name val="Aptos"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="24">
@@ -740,7 +730,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="85">
+  <borders count="87">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1422,7 +1426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1473,75 +1477,114 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="12" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="12" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="23" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="23" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="23" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1631,19 +1674,13 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1658,19 +1695,19 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1685,20 +1722,20 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1706,73 +1743,73 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="17" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1781,10 +1818,10 @@
     <xf numFmtId="0" fontId="16" fillId="17" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="19" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1793,10 +1830,10 @@
     <xf numFmtId="0" fontId="17" fillId="19" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1805,10 +1842,10 @@
     <xf numFmtId="0" fontId="18" fillId="20" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1817,233 +1854,146 @@
     <xf numFmtId="0" fontId="19" fillId="21" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="17" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF55E38D"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF0E4D2D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFD166"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF6A4600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF747A"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF4C1115"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF55E38D"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF173A2A"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFD166"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF6A4600"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF9A9E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF4C1115"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF7A0B10"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="33">
     <dxf>
       <font>
         <b/>
@@ -2074,6 +2024,17 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF0E3B23"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFD86B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7A5200"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2214,6 +2175,17 @@
     <dxf>
       <font>
         <b/>
+        <color rgb="FFFFD86B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7A5200"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -2309,6 +2281,83 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF123421"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF55E38D"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0E4D2D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFD166"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6A4600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF747A"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF4C1115"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF55E38D"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF173A2A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFD166"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6A4600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF9A9E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF4C1115"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7A0B10"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2490,26 +2539,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="45" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
     </row>
     <row r="2" spans="1:11" ht="26.1" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
     </row>
     <row r="3" spans="1:11" ht="9" customHeight="1">
       <c r="A3" s="1"/>
@@ -2521,20 +2570,20 @@
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="I4" s="72" t="s">
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="60"/>
+      <c r="I4" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="73"/>
-      <c r="K4" s="74"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="87"/>
     </row>
     <row r="5" spans="1:11" ht="27" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -2556,11 +2605,11 @@
         <v>9</v>
       </c>
       <c r="G5" s="2"/>
-      <c r="I5" s="75" t="s">
+      <c r="I5" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="76"/>
-      <c r="K5" s="18">
+      <c r="J5" s="89"/>
+      <c r="K5" s="24">
         <f>COUNTIF(D14:D16,"Reply")+COUNTIF(E14:E16,"Online")</f>
         <v>6</v>
       </c>
@@ -2569,19 +2618,19 @@
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="50"/>
-      <c r="I6" s="77" t="s">
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="I6" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="78"/>
-      <c r="K6" s="19">
+      <c r="J6" s="91"/>
+      <c r="K6" s="25">
         <v>6</v>
       </c>
     </row>
@@ -2593,25 +2642,25 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="I7" s="79" t="s">
+      <c r="I7" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="80"/>
-      <c r="K7" s="20">
+      <c r="J7" s="93"/>
+      <c r="K7" s="26">
         <f>K5/K6</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="47"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="60"/>
     </row>
     <row r="9" spans="1:11" ht="27.95" customHeight="1">
       <c r="A9" s="3" t="s">
@@ -2633,68 +2682,68 @@
         <v>21</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="I9" s="81" t="s">
+      <c r="I9" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="82"/>
-      <c r="K9" s="83"/>
+      <c r="J9" s="95"/>
+      <c r="K9" s="96"/>
     </row>
     <row r="10" spans="1:11" ht="27.95" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="50"/>
-      <c r="I10" s="21" t="s">
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="63"/>
+      <c r="I10" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="84" t="str">
-        <f>IF(AND(D14="Reply",E14="Online"),"OK",IF(D14&lt;&gt;"Reply","NETWORK ISSUE","FUNCTION ISSUE"))</f>
+      <c r="J10" s="97" t="str">
+        <f>IF(OR(D14="",E14="",D14="Not Tested",E14="Not Tested"),"CHECK REQUIRED",IF(D14="No Reply","NETWORK ISSUE",IF(E14="Offline","FUNCTION ISSUE","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="K10" s="85"/>
+      <c r="K10" s="98"/>
     </row>
     <row r="11" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A11" s="170"/>
-      <c r="B11" s="170"/>
-      <c r="C11" s="170"/>
-      <c r="D11" s="170"/>
-      <c r="E11" s="170"/>
-      <c r="F11" s="170"/>
-      <c r="G11" s="170"/>
-      <c r="I11" s="22" t="s">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="86" t="str">
-        <f>IF(AND(D15="Reply",E15="Online"),"OK",IF(D15&lt;&gt;"Reply","NETWORK ISSUE","FUNCTION ISSUE"))</f>
+      <c r="J11" s="99" t="str">
+        <f>IF(OR(D15="",E15="",D15="Not Tested",E15="Not Tested"),"CHECK REQUIRED",IF(D15="No Reply","NETWORK ISSUE",IF(E15="Offline","FUNCTION ISSUE","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="K11" s="87"/>
+      <c r="K11" s="100"/>
     </row>
     <row r="12" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47"/>
-      <c r="I12" s="23" t="s">
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="60"/>
+      <c r="I12" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="88" t="str">
-        <f>IF(AND(D16="Reply",E16="Online"),"OK",IF(D16&lt;&gt;"Reply","NETWORK ISSUE","FUNCTION ISSUE"))</f>
+      <c r="J12" s="101" t="str">
+        <f>IF(OR(D16="",E16="",D16="Not Tested",E16="Not Tested"),"CHECK REQUIRED",IF(D16="No Reply","NETWORK ISSUE",IF(E16="Offline","FUNCTION ISSUE","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="K12" s="89"/>
+      <c r="K12" s="102"/>
     </row>
     <row r="13" spans="1:11" ht="36" customHeight="1">
       <c r="A13" s="5" t="s">
@@ -2739,11 +2788,11 @@
         <v>40</v>
       </c>
       <c r="G14" s="11"/>
-      <c r="I14" s="90" t="s">
+      <c r="I14" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="J14" s="91"/>
-      <c r="K14" s="92"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="105"/>
     </row>
     <row r="15" spans="1:11" ht="33" customHeight="1">
       <c r="A15" s="17" t="s">
@@ -2765,12 +2814,12 @@
         <v>44</v>
       </c>
       <c r="G15" s="15"/>
-      <c r="I15" s="93" t="str">
+      <c r="I15" s="106" t="str">
         <f>IF(D18="READY FOR SCREENING","PROCEED WITH SCREENING","CHECK THE FAILED DEVICE ABOVE")</f>
         <v>PROCEED WITH SCREENING</v>
       </c>
-      <c r="J15" s="94"/>
-      <c r="K15" s="95"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="108"/>
     </row>
     <row r="16" spans="1:11" ht="33" customHeight="1">
       <c r="A16" s="16" t="s">
@@ -2792,9 +2841,9 @@
         <v>47</v>
       </c>
       <c r="G16" s="11"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="98"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="111"/>
     </row>
     <row r="17" spans="1:11" ht="9" customHeight="1">
       <c r="A17" s="1"/>
@@ -2804,23 +2853,23 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="I17" s="99"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="101"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="114"/>
     </row>
     <row r="18" spans="1:11" ht="44.1" customHeight="1">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="52"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="54" t="str">
+      <c r="B18" s="65"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="67" t="str">
         <f>IF(AND(B5&lt;&gt;"",D5&lt;&gt;"",F5&lt;&gt;"",B6&lt;&gt;"",D14="Reply",D15="Reply",D16="Reply",E14="Online",E15="Online",E16="Online"),"READY FOR SCREENING","NOT READY - TECHNICAL CHECK REQUIRED")</f>
         <v>READY FOR SCREENING</v>
       </c>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="56"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="69"/>
     </row>
     <row r="19" spans="1:11" ht="9" customHeight="1">
       <c r="A19" s="1"/>
@@ -2832,35 +2881,35 @@
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="47"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="60"/>
     </row>
     <row r="21" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="59"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="72"/>
     </row>
     <row r="22" spans="1:11" ht="30.95" customHeight="1">
-      <c r="A22" s="60"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="62"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="75"/>
     </row>
     <row r="23" spans="1:11" ht="9" customHeight="1">
       <c r="A23" s="1"/>
@@ -2872,85 +2921,83 @@
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="65"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="78"/>
     </row>
     <row r="26" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A26" s="66"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="68"/>
+      <c r="A26" s="79"/>
+      <c r="B26" s="80"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="81"/>
     </row>
     <row r="27" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A27" s="66"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="68"/>
+      <c r="A27" s="79"/>
+      <c r="B27" s="80"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="81"/>
     </row>
     <row r="28" spans="1:11" ht="21.95" customHeight="1">
-      <c r="A28" s="69"/>
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="71"/>
+      <c r="A28" s="82"/>
+      <c r="B28" s="83"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="84"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="66"/>
-      <c r="B29" s="66"/>
-      <c r="C29" s="66"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="66"/>
-      <c r="G29" s="66"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="66"/>
-      <c r="B30" s="66"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="66"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="66"/>
-      <c r="B31" s="66"/>
-      <c r="C31" s="66"/>
-      <c r="D31" s="66"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="66"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A11:G11"/>
+  <mergeCells count="23">
     <mergeCell ref="A21:G22"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A25:G28"/>
@@ -2976,48 +3023,53 @@
     <mergeCell ref="A8:G8"/>
   </mergeCells>
   <conditionalFormatting sqref="D14:D16">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>D14="Reply"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="24" priority="2">
       <formula>D14="No Reply"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="23" priority="3">
       <formula>D14="Not Tested"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:G18">
-    <cfRule type="expression" dxfId="15" priority="6">
+    <cfRule type="expression" dxfId="22" priority="6">
       <formula>D18="READY FOR SCREENING"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="7">
+    <cfRule type="expression" dxfId="21" priority="7">
       <formula>D18="NOT READY - TECHNICAL CHECK REQUIRED"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E16">
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="20" priority="4">
       <formula>E14="Online"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="5">
+    <cfRule type="expression" dxfId="19" priority="5">
       <formula>E14="Offline"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15:K17">
-    <cfRule type="expression" dxfId="11" priority="18">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>I15="PROCEED WITH SCREENING"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="19">
+    <cfRule type="expression" dxfId="17" priority="19">
       <formula>I15="CHECK THE FAILED DEVICE ABOVE"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J10:J12">
+    <cfRule type="expression" dxfId="16" priority="20">
+      <formula>J10="CHECK REQUIRED"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J10:K12">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="15" priority="9">
       <formula>J10="OK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>J10="NETWORK ISSUE"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="11">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>J10="FUNCTION ISSUE"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3032,7 +3084,7 @@
       <formula1>"Reply,No Reply,Not Tested"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E14:E16" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>"Online,Offline"</formula1>
+      <formula1>"Online,Offline,Not Tested"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3052,207 +3104,200 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="115" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="116" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="171"/>
-      <c r="B3" s="171"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="24" t="s">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="104" t="s">
+      <c r="G3" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="105"/>
+      <c r="H3" s="118"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="171"/>
-      <c r="B4" s="171"/>
-      <c r="C4" s="171"/>
-      <c r="D4" s="171"/>
-      <c r="E4" s="171"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="107"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="120"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="93" t="s">
+      <c r="B5" s="108"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="95"/>
-      <c r="F5" s="171"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
     </row>
     <row r="6" spans="1:8" ht="30">
-      <c r="A6" s="96"/>
-      <c r="B6" s="98"/>
-      <c r="C6" s="25" t="s">
+      <c r="A6" s="109"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="96"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="24" t="s">
+      <c r="D6" s="109"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="104" t="s">
+      <c r="G6" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="105"/>
+      <c r="H6" s="118"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="99"/>
-      <c r="B7" s="101"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="107"/>
+      <c r="A7" s="112"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="120"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="171"/>
-      <c r="B8" s="171"/>
-      <c r="C8" s="171"/>
-      <c r="D8" s="171"/>
-      <c r="E8" s="171"/>
-      <c r="F8" s="171"/>
-      <c r="G8" s="171"/>
-      <c r="H8" s="171"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="171"/>
-      <c r="B9" s="171"/>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="24" t="s">
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="104" t="s">
+      <c r="G9" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="105"/>
+      <c r="H9" s="118"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="171"/>
-      <c r="B10" s="171"/>
-      <c r="C10" s="171"/>
-      <c r="D10" s="171"/>
-      <c r="E10" s="171"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="107"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="120"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="171"/>
-      <c r="B11" s="171"/>
-      <c r="C11" s="171"/>
-      <c r="D11" s="171"/>
-      <c r="E11" s="171"/>
-      <c r="F11" s="171"/>
-      <c r="G11" s="171"/>
-      <c r="H11" s="171"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
     </row>
     <row r="12" spans="1:8" ht="15">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-    </row>
-    <row r="13" spans="1:8" ht="25.5">
-      <c r="A13" s="26" t="s">
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+    </row>
+    <row r="13" spans="1:8" ht="25.5" customHeight="1">
+      <c r="A13" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="188" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="169" t="s">
+      <c r="F13" s="189" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="108" t="s">
+      <c r="B14" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="109"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="109"/>
-      <c r="G14" s="109"/>
-      <c r="H14" s="110"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="123"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="171"/>
-      <c r="B15" s="171"/>
-      <c r="C15" s="171"/>
-      <c r="D15" s="171"/>
-      <c r="E15" s="171"/>
-      <c r="F15" s="171"/>
-      <c r="G15" s="171"/>
-      <c r="H15" s="171"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F5:H5"/>
+  <mergeCells count="9">
     <mergeCell ref="G9:H10"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A3:E4"/>
-    <mergeCell ref="A8:E11"/>
-    <mergeCell ref="F11:H11"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B7"/>
@@ -3266,7 +3311,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3280,406 +3325,453 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="124" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="112"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
     </row>
     <row r="3" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A3" s="174" t="s">
+      <c r="A3" s="126" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="174"/>
-      <c r="C3" s="174"/>
-      <c r="D3" s="174"/>
-      <c r="E3" s="174"/>
-      <c r="F3" s="174"/>
-      <c r="G3" s="174"/>
-      <c r="H3" s="174"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
     </row>
     <row r="4" spans="1:8" ht="15">
-      <c r="A4" s="173"/>
-      <c r="B4" s="173"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="115"/>
-      <c r="C5" s="116" t="s">
+      <c r="B5" s="128"/>
+      <c r="C5" s="129" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="117"/>
-      <c r="E5" s="116" t="s">
+      <c r="D5" s="130"/>
+      <c r="E5" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="117"/>
-      <c r="G5" s="116" t="s">
+      <c r="F5" s="130"/>
+      <c r="G5" s="129" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="117"/>
+      <c r="H5" s="130"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="118">
+      <c r="A6" s="131">
         <f>COUNTA(A11:A30)</f>
-        <v>5</v>
-      </c>
-      <c r="B6" s="119"/>
-      <c r="C6" s="122">
+        <v>3</v>
+      </c>
+      <c r="B6" s="132"/>
+      <c r="C6" s="135">
         <f>COUNTIF(G11:G30,"Open")</f>
         <v>1</v>
       </c>
-      <c r="D6" s="123"/>
-      <c r="E6" s="126">
+      <c r="D6" s="136"/>
+      <c r="E6" s="139">
         <f>COUNTIF(G11:G30,"In Progress")</f>
         <v>1</v>
       </c>
-      <c r="F6" s="127"/>
-      <c r="G6" s="130">
+      <c r="F6" s="140"/>
+      <c r="G6" s="143">
         <f>COUNTIF(G11:G30,"Resolved")</f>
         <v>1</v>
       </c>
-      <c r="H6" s="131"/>
+      <c r="H6" s="144"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="120"/>
-      <c r="B7" s="121"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="133"/>
+      <c r="A7" s="133"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="141"/>
+      <c r="F7" s="142"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="146"/>
     </row>
     <row r="8" spans="1:8" ht="15">
-      <c r="A8" s="175"/>
-      <c r="B8" s="175"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
+      <c r="A8" s="36"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:8" ht="24" customHeight="1">
-      <c r="A9" s="134" t="s">
+      <c r="A9" s="147" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="134"/>
-      <c r="C9" s="134"/>
-      <c r="D9" s="134"/>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="134"/>
+      <c r="B9" s="147"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="147"/>
+      <c r="E9" s="147"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="147"/>
+      <c r="H9" s="147"/>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="39" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="52">
         <v>46232</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="H11" s="33" t="s">
+      <c r="H11" s="41" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="53">
         <v>46232</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="G12" s="39" t="s">
+      <c r="G12" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="43" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="53">
         <v>46232</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="35" t="s">
+      <c r="H13" s="43" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A14" s="176"/>
-      <c r="B14" s="176"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="176"/>
-      <c r="H14" s="176"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="43"/>
     </row>
     <row r="15" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A15" s="135" t="s">
+      <c r="A15" s="48"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="43"/>
+    </row>
+    <row r="16" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A16" s="48"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="43"/>
+    </row>
+    <row r="17" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A17" s="48"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="43"/>
+    </row>
+    <row r="18" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A18" s="48"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="43"/>
+    </row>
+    <row r="19" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A19" s="48"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="43"/>
+    </row>
+    <row r="20" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A20" s="48"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="43"/>
+    </row>
+    <row r="21" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A21" s="48"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="43"/>
+    </row>
+    <row r="22" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A22" s="48"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="43"/>
+    </row>
+    <row r="23" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A23" s="48"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="43"/>
+    </row>
+    <row r="24" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A24" s="48"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="43"/>
+    </row>
+    <row r="25" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A25" s="48"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="43"/>
+    </row>
+    <row r="26" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A26" s="48"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="43"/>
+    </row>
+    <row r="27" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A27" s="48"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="43"/>
+    </row>
+    <row r="28" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A28" s="48"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="43"/>
+    </row>
+    <row r="29" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A29" s="48"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="43"/>
+    </row>
+    <row r="30" spans="1:8" ht="38.1" customHeight="1">
+      <c r="A30" s="50"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="45"/>
+    </row>
+    <row r="31" spans="1:8" ht="15">
+      <c r="A31" s="36"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+    </row>
+    <row r="32" spans="1:8" ht="15">
+      <c r="A32" s="148" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="135"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-    </row>
-    <row r="16" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A16" s="177" t="s">
+      <c r="B32" s="148"/>
+      <c r="C32" s="148"/>
+      <c r="D32" s="148"/>
+      <c r="E32" s="148"/>
+      <c r="F32" s="148"/>
+      <c r="G32" s="148"/>
+      <c r="H32" s="148"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="149" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="178"/>
-      <c r="C16" s="178"/>
-      <c r="D16" s="178"/>
-      <c r="E16" s="178"/>
-      <c r="F16" s="178"/>
-      <c r="G16" s="178"/>
-      <c r="H16" s="179"/>
-    </row>
-    <row r="17" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A17" s="177"/>
-      <c r="B17" s="178"/>
-      <c r="C17" s="178"/>
-      <c r="D17" s="178"/>
-      <c r="E17" s="178"/>
-      <c r="F17" s="178"/>
-      <c r="G17" s="178"/>
-      <c r="H17" s="179"/>
-    </row>
-    <row r="18" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A18" s="180"/>
-      <c r="B18" s="181"/>
-      <c r="C18" s="181"/>
-      <c r="D18" s="181"/>
-      <c r="E18" s="181"/>
-      <c r="F18" s="181"/>
-      <c r="G18" s="181"/>
-      <c r="H18" s="182"/>
-    </row>
-    <row r="19" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A19" s="172"/>
-      <c r="B19" s="172"/>
-      <c r="C19" s="172"/>
-      <c r="D19" s="172"/>
-      <c r="E19" s="172"/>
-      <c r="F19" s="172"/>
-      <c r="G19" s="172"/>
-      <c r="H19" s="172"/>
-    </row>
-    <row r="20" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A20" s="172"/>
-      <c r="B20" s="172"/>
-      <c r="C20" s="172"/>
-      <c r="D20" s="172"/>
-      <c r="E20" s="172"/>
-      <c r="F20" s="172"/>
-      <c r="G20" s="172"/>
-      <c r="H20" s="172"/>
-    </row>
-    <row r="21" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A21" s="172"/>
-      <c r="B21" s="172"/>
-      <c r="C21" s="172"/>
-      <c r="D21" s="172"/>
-      <c r="E21" s="172"/>
-      <c r="F21" s="172"/>
-      <c r="G21" s="172"/>
-      <c r="H21" s="172"/>
-    </row>
-    <row r="22" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A22" s="172"/>
-      <c r="B22" s="172"/>
-      <c r="C22" s="172"/>
-      <c r="D22" s="172"/>
-      <c r="E22" s="172"/>
-      <c r="F22" s="172"/>
-      <c r="G22" s="172"/>
-      <c r="H22" s="172"/>
-    </row>
-    <row r="23" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A23" s="172"/>
-      <c r="B23" s="172"/>
-      <c r="C23" s="172"/>
-      <c r="D23" s="172"/>
-      <c r="E23" s="172"/>
-      <c r="F23" s="172"/>
-      <c r="G23" s="172"/>
-      <c r="H23" s="172"/>
-    </row>
-    <row r="24" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A24" s="172"/>
-      <c r="B24" s="172"/>
-      <c r="C24" s="172"/>
-      <c r="D24" s="172"/>
-      <c r="E24" s="172"/>
-      <c r="F24" s="172"/>
-      <c r="G24" s="172"/>
-      <c r="H24" s="172"/>
-    </row>
-    <row r="25" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A25" s="172"/>
-      <c r="B25" s="172"/>
-      <c r="C25" s="172"/>
-      <c r="D25" s="172"/>
-      <c r="E25" s="172"/>
-      <c r="F25" s="172"/>
-      <c r="G25" s="172"/>
-      <c r="H25" s="172"/>
-    </row>
-    <row r="26" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A26" s="172"/>
-      <c r="B26" s="172"/>
-      <c r="C26" s="172"/>
-      <c r="D26" s="172"/>
-      <c r="E26" s="172"/>
-      <c r="F26" s="172"/>
-      <c r="G26" s="172"/>
-      <c r="H26" s="172"/>
-    </row>
-    <row r="27" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A27" s="172"/>
-      <c r="B27" s="172"/>
-      <c r="C27" s="172"/>
-      <c r="D27" s="172"/>
-      <c r="E27" s="172"/>
-      <c r="F27" s="172"/>
-      <c r="G27" s="172"/>
-      <c r="H27" s="172"/>
-    </row>
-    <row r="28" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A28" s="172"/>
-      <c r="B28" s="172"/>
-      <c r="C28" s="172"/>
-      <c r="D28" s="172"/>
-      <c r="E28" s="172"/>
-      <c r="F28" s="172"/>
-      <c r="G28" s="172"/>
-      <c r="H28" s="172"/>
-    </row>
-    <row r="29" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A29" s="172"/>
-      <c r="B29" s="172"/>
-      <c r="C29" s="172"/>
-      <c r="D29" s="172"/>
-      <c r="E29" s="172"/>
-      <c r="F29" s="172"/>
-      <c r="G29" s="172"/>
-      <c r="H29" s="172"/>
-    </row>
-    <row r="30" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A30" s="172"/>
-      <c r="B30" s="172"/>
-      <c r="C30" s="172"/>
-      <c r="D30" s="172"/>
-      <c r="E30" s="172"/>
-      <c r="F30" s="172"/>
-      <c r="G30" s="172"/>
-      <c r="H30" s="172"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="150"/>
+      <c r="D33" s="150"/>
+      <c r="E33" s="150"/>
+      <c r="F33" s="150"/>
+      <c r="G33" s="150"/>
+      <c r="H33" s="151"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="149"/>
+      <c r="B34" s="150"/>
+      <c r="C34" s="150"/>
+      <c r="D34" s="150"/>
+      <c r="E34" s="150"/>
+      <c r="F34" s="150"/>
+      <c r="G34" s="150"/>
+      <c r="H34" s="151"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="152"/>
+      <c r="B35" s="153"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="153"/>
+      <c r="E35" s="153"/>
+      <c r="F35" s="153"/>
+      <c r="G35" s="153"/>
+      <c r="H35" s="154"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H18"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A14:H14"/>
+  <mergeCells count="13">
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H35"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="C6:D7"/>
     <mergeCell ref="E6:F7"/>
@@ -3692,47 +3784,46 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
   </mergeCells>
-  <conditionalFormatting sqref="F11:F13 F15:F30">
-    <cfRule type="expression" dxfId="6" priority="1">
+  <conditionalFormatting sqref="F11:F30">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>F11="Critical"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="31" priority="2">
       <formula>F11="High"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>F11="Medium"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="29" priority="4">
       <formula>F11="Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G13 G15:G30">
-    <cfRule type="expression" dxfId="2" priority="5">
+  <conditionalFormatting sqref="G11:G30">
+    <cfRule type="expression" dxfId="28" priority="5">
       <formula>G11="Open"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6">
+    <cfRule type="expression" dxfId="27" priority="6">
       <formula>G11="In Progress"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="26" priority="7">
       <formula>G11="Resolved"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="C11:C13 C15:C30" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="C11:C30" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Hall 1,Hall 2,Hall 3,Hall 4"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D11:D13 D15:D30" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="D11:D30" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Projector,Sound System,CCTV Camera"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F11:F13 F15:F30" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" sqref="F11:F30" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"Low,Medium,High,Critical"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G11:G13 G15:G30" xr:uid="{00000000-0002-0000-0200-000003000000}">
+    <dataValidation type="list" sqref="G11:G30" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"Open,In Progress,Resolved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3747,540 +3838,540 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="124" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="112"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
     </row>
     <row r="3" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="126" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="113"/>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
+      <c r="B5" s="147"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="147"/>
+      <c r="F5" s="147"/>
+      <c r="G5" s="147"/>
+      <c r="H5" s="147"/>
     </row>
     <row r="6" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A6" s="136" t="s">
+      <c r="A6" s="155" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="137"/>
-      <c r="C6" s="138" t="s">
+      <c r="B6" s="156"/>
+      <c r="C6" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="139"/>
-      <c r="E6" s="139"/>
-      <c r="F6" s="139"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="140"/>
+      <c r="D6" s="158"/>
+      <c r="E6" s="158"/>
+      <c r="F6" s="158"/>
+      <c r="G6" s="158"/>
+      <c r="H6" s="159"/>
     </row>
     <row r="7" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A7" s="136" t="s">
+      <c r="A7" s="155" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="137"/>
-      <c r="C7" s="138" t="s">
+      <c r="B7" s="156"/>
+      <c r="C7" s="157" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="139"/>
-      <c r="E7" s="139"/>
-      <c r="F7" s="139"/>
-      <c r="G7" s="139"/>
-      <c r="H7" s="140"/>
-    </row>
-    <row r="8" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A8" s="136" t="s">
+      <c r="D7" s="158"/>
+      <c r="E7" s="158"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="158"/>
+      <c r="H7" s="159"/>
+    </row>
+    <row r="8" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A8" s="155" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="137"/>
-      <c r="C8" s="138" t="s">
+      <c r="B8" s="156"/>
+      <c r="C8" s="157" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
-      <c r="F8" s="139"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="140"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="159"/>
     </row>
     <row r="9" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A10" s="134" t="s">
+      <c r="A10" s="147" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="134"/>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="134"/>
+      <c r="B10" s="147"/>
+      <c r="C10" s="147"/>
+      <c r="D10" s="147"/>
+      <c r="E10" s="147"/>
+      <c r="F10" s="147"/>
+      <c r="G10" s="147"/>
+      <c r="H10" s="147"/>
     </row>
     <row r="11" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A11" s="141" t="s">
+      <c r="A11" s="160" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="141"/>
-      <c r="C11" s="141"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
+      <c r="B11" s="160"/>
+      <c r="C11" s="160"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
     </row>
     <row r="12" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A12" s="142" t="s">
+      <c r="A12" s="161" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="142"/>
-      <c r="C12" s="142"/>
-      <c r="D12" s="142"/>
-      <c r="E12" s="142"/>
-      <c r="F12" s="142"/>
-      <c r="G12" s="142"/>
-      <c r="H12" s="142"/>
+      <c r="B12" s="161"/>
+      <c r="C12" s="161"/>
+      <c r="D12" s="161"/>
+      <c r="E12" s="161"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="161"/>
+      <c r="H12" s="161"/>
     </row>
     <row r="13" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A13" s="141" t="s">
+      <c r="A13" s="160" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="141"/>
-      <c r="C13" s="141"/>
-      <c r="D13" s="141"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="141"/>
-      <c r="H13" s="141"/>
+      <c r="B13" s="160"/>
+      <c r="C13" s="160"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
     </row>
     <row r="14" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A14" s="142" t="s">
+      <c r="A14" s="161" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="142"/>
-      <c r="C14" s="142"/>
-      <c r="D14" s="142"/>
-      <c r="E14" s="142"/>
-      <c r="F14" s="142"/>
-      <c r="G14" s="142"/>
-      <c r="H14" s="142"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="161"/>
+      <c r="E14" s="161"/>
+      <c r="F14" s="161"/>
+      <c r="G14" s="161"/>
+      <c r="H14" s="161"/>
     </row>
     <row r="15" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A15" s="141" t="s">
+      <c r="A15" s="160" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="141"/>
-      <c r="C15" s="141"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="141"/>
-      <c r="H15" s="141"/>
+      <c r="B15" s="160"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="160"/>
     </row>
     <row r="16" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A16" s="142" t="s">
+      <c r="A16" s="161" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="142"/>
-      <c r="C16" s="142"/>
-      <c r="D16" s="142"/>
-      <c r="E16" s="142"/>
-      <c r="F16" s="142"/>
-      <c r="G16" s="142"/>
-      <c r="H16" s="142"/>
+      <c r="B16" s="161"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
+      <c r="E16" s="161"/>
+      <c r="F16" s="161"/>
+      <c r="G16" s="161"/>
+      <c r="H16" s="161"/>
     </row>
     <row r="17" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
     </row>
     <row r="18" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A18" s="134" t="s">
+      <c r="A18" s="147" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="134"/>
-      <c r="C18" s="134"/>
-      <c r="D18" s="134"/>
-      <c r="E18" s="134"/>
-      <c r="F18" s="134"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="134"/>
+      <c r="B18" s="147"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="147"/>
     </row>
     <row r="19" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A19" s="143" t="s">
+      <c r="A19" s="162" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="144"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="143" t="s">
+      <c r="B19" s="163"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="162" t="s">
         <v>111</v>
       </c>
-      <c r="E19" s="144"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="143" t="s">
+      <c r="E19" s="163"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="162" t="s">
         <v>112</v>
       </c>
-      <c r="H19" s="144"/>
+      <c r="H19" s="163"/>
     </row>
     <row r="20" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="146"/>
-      <c r="C20" s="42" t="s">
+      <c r="A20" s="164"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="145"/>
-      <c r="E20" s="146"/>
-      <c r="F20" s="42" t="s">
+      <c r="D20" s="164"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="145"/>
-      <c r="H20" s="146"/>
+      <c r="G20" s="164"/>
+      <c r="H20" s="165"/>
     </row>
     <row r="21" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A21" s="147"/>
-      <c r="B21" s="148"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="147"/>
-      <c r="H21" s="148"/>
+      <c r="A21" s="166"/>
+      <c r="B21" s="167"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="166"/>
+      <c r="H21" s="167"/>
     </row>
     <row r="22" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="149" t="s">
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="168" t="s">
         <v>113</v>
       </c>
-      <c r="E22" s="149"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="E22" s="168"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
     </row>
     <row r="23" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="162" t="s">
         <v>114</v>
       </c>
-      <c r="B23" s="144"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="143" t="s">
+      <c r="B23" s="163"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="162" t="s">
         <v>115</v>
       </c>
-      <c r="E23" s="144"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="143" t="s">
+      <c r="E23" s="163"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="H23" s="144"/>
+      <c r="H23" s="163"/>
     </row>
     <row r="24" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A24" s="145"/>
-      <c r="B24" s="146"/>
-      <c r="C24" s="42" t="s">
+      <c r="A24" s="164"/>
+      <c r="B24" s="165"/>
+      <c r="C24" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="145"/>
-      <c r="E24" s="146"/>
-      <c r="F24" s="42" t="s">
+      <c r="D24" s="164"/>
+      <c r="E24" s="165"/>
+      <c r="F24" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="G24" s="145"/>
-      <c r="H24" s="146"/>
+      <c r="G24" s="164"/>
+      <c r="H24" s="165"/>
     </row>
     <row r="25" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A25" s="147"/>
-      <c r="B25" s="148"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="147"/>
-      <c r="H25" s="148"/>
+      <c r="A25" s="166"/>
+      <c r="B25" s="167"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="166"/>
+      <c r="E25" s="167"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="166"/>
+      <c r="H25" s="167"/>
     </row>
     <row r="26" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A26" s="28"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
+      <c r="A26" s="36"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
     </row>
     <row r="27" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A27" s="134" t="s">
+      <c r="A27" s="147" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="134"/>
-      <c r="C27" s="134"/>
-      <c r="D27" s="134"/>
-      <c r="E27" s="134"/>
-      <c r="F27" s="134"/>
-      <c r="G27" s="134"/>
-      <c r="H27" s="134"/>
+      <c r="B27" s="147"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="147"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="147"/>
+      <c r="H27" s="147"/>
     </row>
     <row r="28" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A28" s="136" t="s">
+      <c r="A28" s="155" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="150"/>
-      <c r="C28" s="137"/>
-      <c r="D28" s="151" t="s">
+      <c r="B28" s="169"/>
+      <c r="C28" s="156"/>
+      <c r="D28" s="170" t="s">
         <v>119</v>
       </c>
-      <c r="E28" s="152"/>
-      <c r="F28" s="152"/>
-      <c r="G28" s="152"/>
-      <c r="H28" s="153"/>
+      <c r="E28" s="171"/>
+      <c r="F28" s="171"/>
+      <c r="G28" s="171"/>
+      <c r="H28" s="172"/>
     </row>
     <row r="29" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A29" s="136" t="s">
+      <c r="A29" s="155" t="s">
         <v>120</v>
       </c>
-      <c r="B29" s="150"/>
-      <c r="C29" s="137"/>
-      <c r="D29" s="138" t="s">
+      <c r="B29" s="169"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="157" t="s">
         <v>121</v>
       </c>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="140"/>
+      <c r="E29" s="158"/>
+      <c r="F29" s="158"/>
+      <c r="G29" s="158"/>
+      <c r="H29" s="159"/>
     </row>
     <row r="30" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A30" s="136" t="s">
+      <c r="A30" s="155" t="s">
         <v>122</v>
       </c>
-      <c r="B30" s="150"/>
-      <c r="C30" s="137"/>
-      <c r="D30" s="151" t="s">
+      <c r="B30" s="169"/>
+      <c r="C30" s="156"/>
+      <c r="D30" s="170" t="s">
         <v>123</v>
       </c>
-      <c r="E30" s="152"/>
-      <c r="F30" s="152"/>
-      <c r="G30" s="152"/>
-      <c r="H30" s="153"/>
+      <c r="E30" s="171"/>
+      <c r="F30" s="171"/>
+      <c r="G30" s="171"/>
+      <c r="H30" s="172"/>
     </row>
     <row r="31" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A31" s="136" t="s">
+      <c r="A31" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="B31" s="150"/>
-      <c r="C31" s="137"/>
-      <c r="D31" s="138" t="s">
+      <c r="B31" s="169"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="157" t="s">
         <v>125</v>
       </c>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="139"/>
-      <c r="H31" s="140"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="158"/>
+      <c r="G31" s="158"/>
+      <c r="H31" s="159"/>
     </row>
     <row r="32" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A32" s="136" t="s">
+      <c r="A32" s="155" t="s">
         <v>126</v>
       </c>
-      <c r="B32" s="150"/>
-      <c r="C32" s="137"/>
-      <c r="D32" s="151" t="s">
+      <c r="B32" s="169"/>
+      <c r="C32" s="156"/>
+      <c r="D32" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="152"/>
-      <c r="F32" s="152"/>
-      <c r="G32" s="152"/>
-      <c r="H32" s="153"/>
+      <c r="E32" s="171"/>
+      <c r="F32" s="171"/>
+      <c r="G32" s="171"/>
+      <c r="H32" s="172"/>
     </row>
     <row r="33" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A33" s="28"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
+      <c r="A33" s="36"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
     </row>
     <row r="34" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A34" s="134" t="s">
+      <c r="A34" s="147" t="s">
         <v>128</v>
       </c>
-      <c r="B34" s="134"/>
-      <c r="C34" s="134"/>
-      <c r="D34" s="134"/>
-      <c r="E34" s="134"/>
-      <c r="F34" s="134"/>
-      <c r="G34" s="134"/>
-      <c r="H34" s="134"/>
+      <c r="B34" s="147"/>
+      <c r="C34" s="147"/>
+      <c r="D34" s="147"/>
+      <c r="E34" s="147"/>
+      <c r="F34" s="147"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="147"/>
     </row>
     <row r="35" spans="1:8" ht="24" customHeight="1">
-      <c r="A35" s="154" t="s">
+      <c r="A35" s="173" t="s">
         <v>129</v>
       </c>
-      <c r="B35" s="155"/>
-      <c r="C35" s="155"/>
-      <c r="D35" s="155"/>
-      <c r="E35" s="155"/>
-      <c r="F35" s="155"/>
-      <c r="G35" s="155"/>
-      <c r="H35" s="156"/>
+      <c r="B35" s="174"/>
+      <c r="C35" s="174"/>
+      <c r="D35" s="174"/>
+      <c r="E35" s="174"/>
+      <c r="F35" s="174"/>
+      <c r="G35" s="174"/>
+      <c r="H35" s="175"/>
     </row>
     <row r="36" spans="1:8" ht="24" customHeight="1">
-      <c r="A36" s="154"/>
-      <c r="B36" s="155"/>
-      <c r="C36" s="155"/>
-      <c r="D36" s="155"/>
-      <c r="E36" s="155"/>
-      <c r="F36" s="155"/>
-      <c r="G36" s="155"/>
-      <c r="H36" s="156"/>
+      <c r="A36" s="173"/>
+      <c r="B36" s="174"/>
+      <c r="C36" s="174"/>
+      <c r="D36" s="174"/>
+      <c r="E36" s="174"/>
+      <c r="F36" s="174"/>
+      <c r="G36" s="174"/>
+      <c r="H36" s="175"/>
     </row>
     <row r="37" spans="1:8" ht="24" customHeight="1">
-      <c r="A37" s="154"/>
-      <c r="B37" s="155"/>
-      <c r="C37" s="155"/>
-      <c r="D37" s="155"/>
-      <c r="E37" s="155"/>
-      <c r="F37" s="155"/>
-      <c r="G37" s="155"/>
-      <c r="H37" s="156"/>
+      <c r="A37" s="173"/>
+      <c r="B37" s="174"/>
+      <c r="C37" s="174"/>
+      <c r="D37" s="174"/>
+      <c r="E37" s="174"/>
+      <c r="F37" s="174"/>
+      <c r="G37" s="174"/>
+      <c r="H37" s="175"/>
     </row>
     <row r="38" spans="1:8" ht="24" customHeight="1">
-      <c r="A38" s="157"/>
-      <c r="B38" s="158"/>
-      <c r="C38" s="158"/>
-      <c r="D38" s="158"/>
-      <c r="E38" s="158"/>
-      <c r="F38" s="158"/>
-      <c r="G38" s="158"/>
-      <c r="H38" s="159"/>
+      <c r="A38" s="176"/>
+      <c r="B38" s="177"/>
+      <c r="C38" s="177"/>
+      <c r="D38" s="177"/>
+      <c r="E38" s="177"/>
+      <c r="F38" s="177"/>
+      <c r="G38" s="177"/>
+      <c r="H38" s="178"/>
     </row>
     <row r="39" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
+      <c r="A39" s="36"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
     </row>
     <row r="40" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A40" s="134" t="s">
+      <c r="A40" s="147" t="s">
         <v>130</v>
       </c>
-      <c r="B40" s="134"/>
-      <c r="C40" s="134"/>
-      <c r="D40" s="134"/>
-      <c r="E40" s="134"/>
-      <c r="F40" s="134"/>
-      <c r="G40" s="134"/>
-      <c r="H40" s="134"/>
+      <c r="B40" s="147"/>
+      <c r="C40" s="147"/>
+      <c r="D40" s="147"/>
+      <c r="E40" s="147"/>
+      <c r="F40" s="147"/>
+      <c r="G40" s="147"/>
+      <c r="H40" s="147"/>
     </row>
     <row r="41" spans="1:8" ht="24" customHeight="1">
-      <c r="A41" s="160" t="s">
+      <c r="A41" s="179" t="s">
         <v>131</v>
       </c>
-      <c r="B41" s="161"/>
-      <c r="C41" s="161"/>
-      <c r="D41" s="161"/>
-      <c r="E41" s="161"/>
-      <c r="F41" s="161"/>
-      <c r="G41" s="161"/>
-      <c r="H41" s="162"/>
+      <c r="B41" s="180"/>
+      <c r="C41" s="180"/>
+      <c r="D41" s="180"/>
+      <c r="E41" s="180"/>
+      <c r="F41" s="180"/>
+      <c r="G41" s="180"/>
+      <c r="H41" s="181"/>
     </row>
     <row r="42" spans="1:8" ht="24" customHeight="1">
-      <c r="A42" s="163"/>
-      <c r="B42" s="164"/>
-      <c r="C42" s="164"/>
-      <c r="D42" s="164"/>
-      <c r="E42" s="164"/>
-      <c r="F42" s="164"/>
-      <c r="G42" s="164"/>
-      <c r="H42" s="165"/>
+      <c r="A42" s="182"/>
+      <c r="B42" s="183"/>
+      <c r="C42" s="183"/>
+      <c r="D42" s="183"/>
+      <c r="E42" s="183"/>
+      <c r="F42" s="183"/>
+      <c r="G42" s="183"/>
+      <c r="H42" s="184"/>
     </row>
     <row r="43" spans="1:8" ht="24" customHeight="1">
-      <c r="A43" s="163"/>
-      <c r="B43" s="164"/>
-      <c r="C43" s="164"/>
-      <c r="D43" s="164"/>
-      <c r="E43" s="164"/>
-      <c r="F43" s="164"/>
-      <c r="G43" s="164"/>
-      <c r="H43" s="165"/>
+      <c r="A43" s="182"/>
+      <c r="B43" s="183"/>
+      <c r="C43" s="183"/>
+      <c r="D43" s="183"/>
+      <c r="E43" s="183"/>
+      <c r="F43" s="183"/>
+      <c r="G43" s="183"/>
+      <c r="H43" s="184"/>
     </row>
     <row r="44" spans="1:8" ht="24" customHeight="1">
-      <c r="A44" s="166"/>
-      <c r="B44" s="167"/>
-      <c r="C44" s="167"/>
-      <c r="D44" s="167"/>
-      <c r="E44" s="167"/>
-      <c r="F44" s="167"/>
-      <c r="G44" s="167"/>
-      <c r="H44" s="168"/>
+      <c r="A44" s="185"/>
+      <c r="B44" s="186"/>
+      <c r="C44" s="186"/>
+      <c r="D44" s="186"/>
+      <c r="E44" s="186"/>
+      <c r="F44" s="186"/>
+      <c r="G44" s="186"/>
+      <c r="H44" s="187"/>
     </row>
     <row r="45" spans="1:8" ht="15">
-      <c r="A45" s="28"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
+      <c r="A45" s="36"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="39">
